--- a/datos/datos_calidad_aire_DIARIO_ICA.xlsx
+++ b/datos/datos_calidad_aire_DIARIO_ICA.xlsx
@@ -853,9 +853,7 @@
       <c r="AG2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AH2" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH2" s="6" t="inlineStr"/>
       <c r="AI2" s="4" t="n">
         <v>47</v>
       </c>
@@ -974,9 +972,7 @@
       <c r="AG3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AH3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" s="6" t="inlineStr"/>
       <c r="AI3" s="4" t="n">
         <v>39</v>
       </c>
@@ -1097,9 +1093,7 @@
       <c r="AG4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AH4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH4" s="6" t="inlineStr"/>
       <c r="AI4" s="4" t="n">
         <v>33</v>
       </c>
@@ -1216,9 +1210,7 @@
       <c r="AG5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="AH5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH5" s="6" t="inlineStr"/>
       <c r="AI5" s="4" t="n">
         <v>33</v>
       </c>
@@ -1339,9 +1331,7 @@
       <c r="AG6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AH6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH6" s="6" t="inlineStr"/>
       <c r="AI6" s="4" t="n">
         <v>48</v>
       </c>
@@ -13701,9 +13691,7 @@
       <c r="O2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P2" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="4" t="n">
         <v>47</v>
       </c>
@@ -13750,9 +13738,7 @@
       <c r="O3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="4" t="n">
         <v>39</v>
       </c>
@@ -13799,9 +13785,7 @@
       <c r="O4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="4" t="n">
         <v>33</v>
       </c>
@@ -13846,9 +13830,7 @@
       <c r="O5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="4" t="n">
         <v>33</v>
       </c>
@@ -13895,9 +13877,7 @@
       <c r="O6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="4" t="n">
         <v>48</v>
       </c>
@@ -22741,9 +22721,7 @@
       <c r="C2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="D2" s="6" t="inlineStr"/>
       <c r="E2" s="4" t="n">
         <v>47</v>
       </c>
@@ -22762,9 +22740,7 @@
       <c r="C3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="D3" s="6" t="inlineStr"/>
       <c r="E3" s="4" t="n">
         <v>39</v>
       </c>
@@ -22783,9 +22759,7 @@
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="4" t="n">
         <v>33</v>
       </c>
@@ -22804,9 +22778,7 @@
       <c r="C5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="4" t="n">
         <v>33</v>
       </c>
@@ -22825,9 +22797,7 @@
       <c r="C6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="4" t="n">
         <v>48</v>
       </c>

--- a/datos/datos_calidad_aire_DIARIO_ICA.xlsx
+++ b/datos/datos_calidad_aire_DIARIO_ICA.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>9</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>7</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>6</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>5</v>
@@ -1253,7 +1253,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>8</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>7</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>7</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>9</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>9</v>
@@ -1834,7 +1834,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>7</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>4</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>5</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>4</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>7</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>6</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>5</v>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>5</v>
@@ -2998,7 +2998,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>5</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>5</v>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>5</v>
@@ -3333,7 +3333,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>6</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>6</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>5</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>6</v>
@@ -3759,7 +3759,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>4</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>6</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>7</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>6</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>4</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>4</v>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>4</v>
@@ -4590,7 +4590,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>5</v>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>5</v>
@@ -4828,7 +4828,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>4</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>5</v>
@@ -5056,7 +5056,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>4</v>
@@ -5173,7 +5173,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>5</v>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>6</v>
@@ -5415,7 +5415,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>7</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>7</v>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>7</v>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>7</v>
@@ -5883,7 +5883,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>7</v>
@@ -5996,7 +5996,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>6</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>4</v>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>6</v>
@@ -6323,7 +6323,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>7</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>7</v>
@@ -6547,7 +6547,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>8</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>7</v>
@@ -6751,7 +6751,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>3</v>
@@ -6850,7 +6850,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="4" t="n">
         <v>3</v>
@@ -6939,7 +6939,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="4" t="n">
         <v>5</v>
@@ -7036,7 +7036,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
@@ -7139,7 +7139,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="4" t="n">
         <v>6</v>
@@ -7345,7 +7345,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="4" t="n">
         <v>4</v>
@@ -7456,7 +7456,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="4" t="n">
         <v>4</v>
@@ -7569,7 +7569,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="4" t="n">
         <v>4</v>
@@ -7674,7 +7674,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="4" t="n">
         <v>3</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="4" t="n">
         <v>3</v>
@@ -7888,7 +7888,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="4" t="n">
         <v>3</v>
@@ -7989,7 +7989,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="4" t="n">
         <v>4</v>
@@ -8090,7 +8090,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>4</v>
@@ -8203,7 +8203,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>4</v>
@@ -8516,7 +8516,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>9</v>
@@ -8595,7 +8595,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>7</v>
@@ -8672,7 +8672,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>6</v>
@@ -8751,7 +8751,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>5</v>
@@ -8828,7 +8828,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>8</v>
@@ -8907,7 +8907,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>7</v>
@@ -8986,7 +8986,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>7</v>
@@ -9065,7 +9065,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>9</v>
@@ -9144,7 +9144,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>9</v>
@@ -9211,7 +9211,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>7</v>
@@ -9290,7 +9290,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
@@ -9367,7 +9367,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>4</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>5</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>5</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>4</v>
@@ -9677,7 +9677,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>7</v>
@@ -9756,7 +9756,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>6</v>
@@ -9835,7 +9835,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>5</v>
@@ -9914,7 +9914,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>5</v>
@@ -9993,7 +9993,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>5</v>
@@ -10072,7 +10072,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>5</v>
@@ -10151,7 +10151,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>5</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>6</v>
@@ -10283,7 +10283,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>6</v>
@@ -10350,7 +10350,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>5</v>
@@ -10417,7 +10417,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>6</v>
@@ -10484,7 +10484,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>4</v>
@@ -10559,7 +10559,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>6</v>
@@ -10638,7 +10638,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>7</v>
@@ -10717,7 +10717,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>6</v>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>4</v>
@@ -10875,7 +10875,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>4</v>
@@ -10952,7 +10952,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>4</v>
@@ -11029,7 +11029,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>5</v>
@@ -11108,7 +11108,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>5</v>
@@ -11183,7 +11183,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>4</v>
@@ -11258,7 +11258,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>5</v>
@@ -11327,7 +11327,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>4</v>
@@ -11404,7 +11404,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>5</v>
@@ -11485,7 +11485,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>6</v>
@@ -11562,7 +11562,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>7</v>
@@ -11637,7 +11637,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>7</v>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>7</v>
@@ -11791,7 +11791,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>7</v>
@@ -11862,7 +11862,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>7</v>
@@ -11933,7 +11933,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>6</v>
@@ -12000,7 +12000,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>4</v>
@@ -12079,7 +12079,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>6</v>
@@ -12146,7 +12146,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>7</v>
@@ -12213,7 +12213,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>7</v>
@@ -12286,7 +12286,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>8</v>
@@ -12355,7 +12355,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>7</v>
@@ -12424,7 +12424,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>3</v>
@@ -12491,7 +12491,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="4" t="n">
         <v>3</v>
@@ -12558,7 +12558,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="4" t="n">
         <v>5</v>
@@ -12625,7 +12625,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
@@ -12763,7 +12763,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="4" t="n">
         <v>6</v>
@@ -12832,7 +12832,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="4" t="n">
         <v>4</v>
@@ -12911,7 +12911,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="4" t="n">
         <v>4</v>
@@ -12992,7 +12992,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="4" t="n">
         <v>4</v>
@@ -13073,7 +13073,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="4" t="n">
         <v>3</v>
@@ -13152,7 +13152,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="4" t="n">
         <v>3</v>
@@ -13233,7 +13233,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="4" t="n">
         <v>3</v>
@@ -13300,7 +13300,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="4" t="n">
         <v>4</v>
@@ -13367,7 +13367,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>4</v>
@@ -13446,7 +13446,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>4</v>
@@ -13657,7 +13657,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="6" t="inlineStr"/>
       <c r="C2" s="6" t="inlineStr"/>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="6" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr"/>
@@ -13749,7 +13749,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="6" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr"/>
@@ -13796,7 +13796,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr"/>
@@ -13841,7 +13841,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
@@ -13888,7 +13888,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="6" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr"/>
@@ -13933,7 +13933,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="6" t="inlineStr"/>
@@ -13974,7 +13974,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="6" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr"/>
@@ -14021,7 +14021,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr"/>
@@ -14064,7 +14064,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="6" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr"/>
@@ -14107,7 +14107,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr"/>
@@ -14148,7 +14148,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr"/>
@@ -14187,7 +14187,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
@@ -14230,7 +14230,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="6" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr"/>
@@ -14271,7 +14271,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr"/>
@@ -14312,7 +14312,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="6" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr"/>
@@ -14359,7 +14359,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="6" t="inlineStr"/>
       <c r="C18" s="6" t="inlineStr"/>
@@ -14406,7 +14406,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="6" t="inlineStr"/>
       <c r="C19" s="6" t="inlineStr"/>
@@ -14451,7 +14451,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="6" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr"/>
@@ -14496,7 +14496,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr"/>
@@ -14539,7 +14539,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
@@ -14623,7 +14623,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
@@ -14668,7 +14668,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="6" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr"/>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="6" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr"/>
@@ -14756,7 +14756,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="6" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr"/>
@@ -14801,7 +14801,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="6" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr"/>
@@ -14842,7 +14842,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="6" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="6" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr"/>
@@ -14936,7 +14936,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="6" t="inlineStr"/>
       <c r="C31" s="6" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="6" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr"/>
@@ -15030,7 +15030,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="6" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="6" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr"/>
@@ -15122,7 +15122,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="6" t="inlineStr"/>
       <c r="C35" s="6" t="inlineStr"/>
@@ -15169,7 +15169,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="6" t="inlineStr"/>
       <c r="C36" s="6" t="inlineStr"/>
@@ -15216,7 +15216,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="6" t="inlineStr"/>
       <c r="C37" s="6" t="inlineStr"/>
@@ -15263,7 +15263,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="6" t="inlineStr"/>
       <c r="C38" s="6" t="inlineStr"/>
@@ -15310,7 +15310,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="6" t="inlineStr"/>
       <c r="C39" s="6" t="inlineStr"/>
@@ -15355,7 +15355,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="6" t="inlineStr"/>
       <c r="C40" s="6" t="inlineStr"/>
@@ -15402,7 +15402,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="6" t="inlineStr"/>
       <c r="C41" s="6" t="inlineStr"/>
@@ -15449,7 +15449,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="6" t="inlineStr"/>
       <c r="C42" s="6" t="inlineStr"/>
@@ -15496,7 +15496,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="6" t="inlineStr"/>
       <c r="C43" s="6" t="inlineStr"/>
@@ -15543,7 +15543,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="6" t="inlineStr"/>
       <c r="C44" s="6" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="6" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr"/>
@@ -15637,7 +15637,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="6" t="inlineStr"/>
       <c r="C46" s="6" t="inlineStr"/>
@@ -15684,7 +15684,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="6" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr"/>
@@ -15729,7 +15729,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="6" t="inlineStr"/>
       <c r="C48" s="6" t="inlineStr"/>
@@ -15766,7 +15766,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="6" t="inlineStr"/>
       <c r="C49" s="6" t="inlineStr"/>
@@ -15813,7 +15813,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="6" t="inlineStr"/>
       <c r="C50" s="6" t="inlineStr"/>
@@ -15860,7 +15860,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="6" t="inlineStr"/>
       <c r="C51" s="6" t="inlineStr"/>
@@ -15907,7 +15907,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="6" t="inlineStr"/>
       <c r="C52" s="6" t="inlineStr"/>
@@ -15946,7 +15946,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="6" t="inlineStr"/>
       <c r="C53" s="6" t="inlineStr"/>
@@ -15983,7 +15983,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="6" t="inlineStr"/>
       <c r="C54" s="6" t="inlineStr"/>
@@ -16020,7 +16020,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="6" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr"/>
@@ -16047,7 +16047,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="6" t="inlineStr"/>
       <c r="C56" s="6" t="inlineStr"/>
@@ -16082,7 +16082,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="6" t="inlineStr"/>
       <c r="C57" s="6" t="inlineStr"/>
@@ -16121,7 +16121,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="6" t="inlineStr"/>
       <c r="C58" s="6" t="inlineStr"/>
@@ -16160,7 +16160,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="6" t="inlineStr"/>
       <c r="C59" s="6" t="inlineStr"/>
@@ -16199,7 +16199,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="6" t="inlineStr"/>
       <c r="C60" s="6" t="inlineStr"/>
@@ -16236,7 +16236,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="6" t="inlineStr"/>
       <c r="C61" s="6" t="inlineStr"/>
@@ -16273,7 +16273,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="6" t="inlineStr"/>
       <c r="C62" s="6" t="inlineStr"/>
@@ -16302,7 +16302,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="6" t="inlineStr"/>
       <c r="C63" s="6" t="inlineStr"/>
@@ -16331,7 +16331,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="6" t="inlineStr"/>
       <c r="C64" s="6" t="inlineStr"/>
@@ -16366,7 +16366,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="6" t="inlineStr"/>
       <c r="C65" s="6" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="6" t="inlineStr"/>
       <c r="C66" s="6" t="inlineStr"/>
@@ -16444,7 +16444,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="6" t="inlineStr"/>
       <c r="C67" s="6" t="inlineStr"/>
@@ -16483,7 +16483,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="6" t="inlineStr"/>
       <c r="C68" s="6" t="inlineStr"/>
@@ -16578,7 +16578,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>9</v>
@@ -16601,7 +16601,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>7</v>
@@ -16624,7 +16624,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>6</v>
@@ -16647,7 +16647,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>5</v>
@@ -16670,7 +16670,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>8</v>
@@ -16693,7 +16693,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>7</v>
@@ -16716,7 +16716,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>7</v>
@@ -16739,7 +16739,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>9</v>
@@ -16762,7 +16762,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>9</v>
@@ -16785,7 +16785,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>7</v>
@@ -16808,7 +16808,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4</v>
@@ -16831,7 +16831,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>4</v>
@@ -16854,7 +16854,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>5</v>
@@ -16877,7 +16877,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>5</v>
@@ -16900,7 +16900,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>4</v>
@@ -16923,7 +16923,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>7</v>
@@ -16946,7 +16946,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>6</v>
@@ -16969,7 +16969,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>5</v>
@@ -16992,7 +16992,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>5</v>
@@ -17015,7 +17015,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>5</v>
@@ -17038,7 +17038,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>5</v>
@@ -17061,7 +17061,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>5</v>
@@ -17084,7 +17084,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>6</v>
@@ -17107,7 +17107,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>6</v>
@@ -17130,7 +17130,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>5</v>
@@ -17153,7 +17153,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>6</v>
@@ -17176,7 +17176,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>4</v>
@@ -17197,7 +17197,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>6</v>
@@ -17220,7 +17220,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>7</v>
@@ -17243,7 +17243,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>6</v>
@@ -17266,7 +17266,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>4</v>
@@ -17289,7 +17289,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>4</v>
@@ -17312,7 +17312,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>4</v>
@@ -17335,7 +17335,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>5</v>
@@ -17358,7 +17358,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>5</v>
@@ -17381,7 +17381,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>4</v>
@@ -17402,7 +17402,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>5</v>
@@ -17425,7 +17425,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>4</v>
@@ -17446,7 +17446,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>5</v>
@@ -17469,7 +17469,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>6</v>
@@ -17492,7 +17492,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>7</v>
@@ -17515,7 +17515,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>7</v>
@@ -17536,7 +17536,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>7</v>
@@ -17557,7 +17557,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>7</v>
@@ -17580,7 +17580,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>7</v>
@@ -17603,7 +17603,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>6</v>
@@ -17626,7 +17626,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>4</v>
@@ -17649,7 +17649,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>6</v>
@@ -17672,7 +17672,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>7</v>
@@ -17693,7 +17693,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>7</v>
@@ -17716,7 +17716,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>8</v>
@@ -17739,7 +17739,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>7</v>
@@ -17762,7 +17762,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>3</v>
@@ -17785,7 +17785,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="4" t="n">
         <v>3</v>
@@ -17808,7 +17808,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="4" t="n">
         <v>5</v>
@@ -17831,7 +17831,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="4" t="n">
         <v>7</v>
@@ -17854,7 +17854,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="4" t="n">
         <v>7</v>
@@ -17877,7 +17877,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="4" t="n">
         <v>6</v>
@@ -17900,7 +17900,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="4" t="n">
         <v>4</v>
@@ -17923,7 +17923,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="4" t="n">
         <v>4</v>
@@ -17946,7 +17946,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="4" t="n">
         <v>4</v>
@@ -17969,7 +17969,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="4" t="n">
         <v>3</v>
@@ -17992,7 +17992,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="4" t="n">
         <v>3</v>
@@ -18015,7 +18015,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="4" t="n">
         <v>3</v>
@@ -18038,7 +18038,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="4" t="n">
         <v>4</v>
@@ -18059,7 +18059,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>4</v>
@@ -18080,7 +18080,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>4</v>
@@ -18161,7 +18161,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="6" t="inlineStr"/>
       <c r="C2" s="6" t="inlineStr"/>
@@ -18176,7 +18176,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="6" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr"/>
@@ -18191,7 +18191,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="6" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr"/>
@@ -18206,7 +18206,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr"/>
@@ -18219,7 +18219,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
@@ -18234,7 +18234,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="6" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr"/>
@@ -18247,7 +18247,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="6" t="inlineStr"/>
@@ -18260,7 +18260,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="6" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr"/>
@@ -18275,7 +18275,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr"/>
@@ -18288,7 +18288,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="6" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr"/>
@@ -18301,7 +18301,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr"/>
@@ -18312,7 +18312,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr"/>
@@ -18323,7 +18323,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
@@ -18336,7 +18336,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="6" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr"/>
@@ -18349,7 +18349,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr"/>
@@ -18362,7 +18362,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="6" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr"/>
@@ -18375,7 +18375,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="6" t="inlineStr"/>
       <c r="C18" s="6" t="inlineStr"/>
@@ -18388,7 +18388,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="6" t="inlineStr"/>
       <c r="C19" s="6" t="inlineStr"/>
@@ -18401,7 +18401,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="6" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr"/>
@@ -18414,7 +18414,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr"/>
@@ -18427,7 +18427,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
@@ -18438,7 +18438,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
@@ -18449,7 +18449,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
@@ -18462,7 +18462,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="6" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr"/>
@@ -18475,7 +18475,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="6" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr"/>
@@ -18488,7 +18488,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="6" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr"/>
@@ -18501,7 +18501,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="6" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr"/>
@@ -18512,7 +18512,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="6" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr"/>
@@ -18525,7 +18525,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="6" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr"/>
@@ -18538,7 +18538,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="6" t="inlineStr"/>
       <c r="C31" s="6" t="inlineStr"/>
@@ -18551,7 +18551,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="6" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr"/>
@@ -18564,7 +18564,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="6" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr"/>
@@ -18577,7 +18577,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="6" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr"/>
@@ -18590,7 +18590,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="6" t="inlineStr"/>
       <c r="C35" s="6" t="inlineStr"/>
@@ -18603,7 +18603,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="6" t="inlineStr"/>
       <c r="C36" s="6" t="inlineStr"/>
@@ -18616,7 +18616,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="6" t="inlineStr"/>
       <c r="C37" s="6" t="inlineStr"/>
@@ -18629,7 +18629,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="6" t="inlineStr"/>
       <c r="C38" s="6" t="inlineStr"/>
@@ -18642,7 +18642,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="6" t="inlineStr"/>
       <c r="C39" s="6" t="inlineStr"/>
@@ -18655,7 +18655,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="6" t="inlineStr"/>
       <c r="C40" s="6" t="inlineStr"/>
@@ -18668,7 +18668,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="6" t="inlineStr"/>
       <c r="C41" s="6" t="inlineStr"/>
@@ -18681,7 +18681,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="6" t="inlineStr"/>
       <c r="C42" s="6" t="inlineStr"/>
@@ -18694,7 +18694,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="6" t="inlineStr"/>
       <c r="C43" s="6" t="inlineStr"/>
@@ -18707,7 +18707,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="6" t="inlineStr"/>
       <c r="C44" s="6" t="inlineStr"/>
@@ -18720,7 +18720,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="6" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr"/>
@@ -18733,7 +18733,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="6" t="inlineStr"/>
       <c r="C46" s="6" t="inlineStr"/>
@@ -18746,7 +18746,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="6" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr"/>
@@ -18759,7 +18759,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="6" t="inlineStr"/>
       <c r="C48" s="6" t="inlineStr"/>
@@ -18772,7 +18772,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="6" t="inlineStr"/>
       <c r="C49" s="6" t="inlineStr"/>
@@ -18785,7 +18785,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="6" t="inlineStr"/>
       <c r="C50" s="6" t="inlineStr"/>
@@ -18798,7 +18798,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="6" t="inlineStr"/>
       <c r="C51" s="6" t="inlineStr"/>
@@ -18811,7 +18811,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="6" t="inlineStr"/>
       <c r="C52" s="6" t="inlineStr"/>
@@ -18824,7 +18824,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="6" t="inlineStr"/>
       <c r="C53" s="6" t="inlineStr"/>
@@ -18837,7 +18837,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="6" t="inlineStr"/>
       <c r="C54" s="6" t="inlineStr"/>
@@ -18850,7 +18850,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="6" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr"/>
@@ -18861,7 +18861,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="6" t="inlineStr"/>
       <c r="C56" s="6" t="inlineStr"/>
@@ -18872,7 +18872,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="6" t="inlineStr"/>
       <c r="C57" s="6" t="inlineStr"/>
@@ -18885,7 +18885,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="6" t="inlineStr"/>
       <c r="C58" s="6" t="inlineStr"/>
@@ -18898,7 +18898,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="6" t="inlineStr"/>
       <c r="C59" s="6" t="inlineStr"/>
@@ -18911,7 +18911,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="6" t="inlineStr"/>
       <c r="C60" s="6" t="inlineStr"/>
@@ -18924,7 +18924,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="6" t="inlineStr"/>
       <c r="C61" s="6" t="inlineStr"/>
@@ -18937,7 +18937,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="6" t="inlineStr"/>
       <c r="C62" s="6" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="6" t="inlineStr"/>
       <c r="C63" s="6" t="inlineStr"/>
@@ -18963,7 +18963,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="6" t="inlineStr"/>
       <c r="C64" s="6" t="inlineStr"/>
@@ -18976,7 +18976,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="6" t="inlineStr"/>
       <c r="C65" s="6" t="inlineStr"/>
@@ -18989,7 +18989,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="6" t="inlineStr"/>
       <c r="C66" s="6" t="inlineStr"/>
@@ -19002,7 +19002,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="6" t="inlineStr"/>
       <c r="C67" s="6" t="inlineStr"/>
@@ -19015,7 +19015,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="6" t="inlineStr"/>
       <c r="C68" s="6" t="inlineStr"/>
@@ -19088,7 +19088,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>15</v>
@@ -19111,7 +19111,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>12</v>
@@ -19132,7 +19132,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>11</v>
@@ -19155,7 +19155,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>10</v>
@@ -19176,7 +19176,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>13</v>
@@ -19199,7 +19199,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>12</v>
@@ -19222,7 +19222,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>12</v>
@@ -19245,7 +19245,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>15</v>
@@ -19268,7 +19268,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr"/>
@@ -19279,7 +19279,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>13</v>
@@ -19302,7 +19302,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>10</v>
@@ -19323,7 +19323,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>12</v>
@@ -19346,7 +19346,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>13</v>
@@ -19367,7 +19367,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
@@ -19388,7 +19388,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>11</v>
@@ -19409,7 +19409,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>14</v>
@@ -19432,7 +19432,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>14</v>
@@ -19455,7 +19455,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>12</v>
@@ -19478,7 +19478,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>14</v>
@@ -19501,7 +19501,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>14</v>
@@ -19524,7 +19524,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>13</v>
@@ -19547,7 +19547,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>12</v>
@@ -19568,7 +19568,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
@@ -19579,7 +19579,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="6" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr"/>
@@ -19590,7 +19590,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="6" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr"/>
@@ -19601,7 +19601,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="6" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr"/>
@@ -19612,7 +19612,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>12</v>
@@ -19633,7 +19633,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>14</v>
@@ -19656,7 +19656,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>15</v>
@@ -19679,7 +19679,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>14</v>
@@ -19702,7 +19702,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>12</v>
@@ -19725,7 +19725,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>12</v>
@@ -19748,7 +19748,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>12</v>
@@ -19771,7 +19771,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>13</v>
@@ -19794,7 +19794,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>13</v>
@@ -19813,7 +19813,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>12</v>
@@ -19834,7 +19834,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>14</v>
@@ -19857,7 +19857,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>12</v>
@@ -19880,7 +19880,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>13</v>
@@ -19903,7 +19903,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="6" t="inlineStr"/>
       <c r="C41" s="4" t="n">
@@ -19924,7 +19924,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="6" t="inlineStr"/>
       <c r="C42" s="4" t="n">
@@ -19943,7 +19943,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>6</v>
@@ -19966,7 +19966,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>7</v>
@@ -19989,7 +19989,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="6" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr"/>
@@ -20004,7 +20004,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="6" t="inlineStr"/>
       <c r="C46" s="6" t="inlineStr"/>
@@ -20019,7 +20019,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="6" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr"/>
@@ -20030,7 +20030,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>6</v>
@@ -20053,7 +20053,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="6" t="inlineStr"/>
       <c r="C49" s="6" t="inlineStr"/>
@@ -20064,7 +20064,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="6" t="inlineStr"/>
       <c r="C50" s="6" t="inlineStr"/>
@@ -20075,7 +20075,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="6" t="inlineStr"/>
       <c r="C51" s="6" t="inlineStr"/>
@@ -20090,7 +20090,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="6" t="inlineStr"/>
       <c r="C52" s="6" t="inlineStr"/>
@@ -20101,7 +20101,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="6" t="inlineStr"/>
       <c r="C53" s="6" t="inlineStr"/>
@@ -20112,7 +20112,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="6" t="inlineStr"/>
       <c r="C54" s="6" t="inlineStr"/>
@@ -20123,7 +20123,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="6" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr"/>
@@ -20134,7 +20134,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="6" t="inlineStr"/>
       <c r="C56" s="6" t="inlineStr"/>
@@ -20145,7 +20145,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="6" t="inlineStr"/>
       <c r="C57" s="6" t="inlineStr"/>
@@ -20156,7 +20156,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="6" t="inlineStr"/>
       <c r="C58" s="6" t="inlineStr"/>
@@ -20167,7 +20167,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="6" t="inlineStr"/>
       <c r="C59" s="6" t="inlineStr"/>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="4" t="n">
         <v>6</v>
@@ -20199,7 +20199,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="4" t="n">
         <v>7</v>
@@ -20222,7 +20222,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="4" t="n">
         <v>7</v>
@@ -20245,7 +20245,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="4" t="n">
         <v>6</v>
@@ -20268,7 +20268,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="4" t="n">
         <v>6</v>
@@ -20291,7 +20291,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="4" t="n">
         <v>6</v>
@@ -20314,7 +20314,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="4" t="n">
         <v>7</v>
@@ -20337,7 +20337,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>7</v>
@@ -20360,7 +20360,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>7</v>
@@ -20443,7 +20443,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="6" t="inlineStr"/>
       <c r="C2" s="6" t="inlineStr"/>
@@ -20454,7 +20454,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="6" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr"/>
@@ -20465,7 +20465,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="6" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr"/>
@@ -20476,7 +20476,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="6" t="inlineStr"/>
       <c r="C5" s="6" t="inlineStr"/>
@@ -20487,7 +20487,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="6" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
@@ -20498,7 +20498,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="6" t="inlineStr"/>
       <c r="C7" s="6" t="inlineStr"/>
@@ -20509,7 +20509,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="6" t="inlineStr"/>
@@ -20520,7 +20520,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="6" t="inlineStr"/>
       <c r="C9" s="6" t="inlineStr"/>
@@ -20531,7 +20531,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="6" t="inlineStr"/>
@@ -20542,7 +20542,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="6" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr"/>
@@ -20553,7 +20553,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr"/>
@@ -20564,7 +20564,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
       <c r="C13" s="6" t="inlineStr"/>
@@ -20575,7 +20575,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="6" t="inlineStr"/>
       <c r="C14" s="6" t="inlineStr"/>
@@ -20586,7 +20586,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="6" t="inlineStr"/>
       <c r="C15" s="6" t="inlineStr"/>
@@ -20597,7 +20597,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr"/>
@@ -20608,7 +20608,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="6" t="inlineStr"/>
       <c r="C17" s="6" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="6" t="inlineStr"/>
       <c r="C18" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="6" t="inlineStr"/>
       <c r="C19" s="6" t="inlineStr"/>
@@ -20641,7 +20641,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="6" t="inlineStr"/>
       <c r="C20" s="6" t="inlineStr"/>
@@ -20652,7 +20652,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="6" t="inlineStr"/>
       <c r="C21" s="6" t="inlineStr"/>
@@ -20663,7 +20663,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="6" t="inlineStr"/>
       <c r="C22" s="6" t="inlineStr"/>
@@ -20674,7 +20674,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
@@ -20685,7 +20685,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
@@ -20696,7 +20696,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="6" t="inlineStr"/>
       <c r="C25" s="6" t="inlineStr"/>
@@ -20707,7 +20707,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="6" t="inlineStr"/>
       <c r="C26" s="6" t="inlineStr"/>
@@ -20718,7 +20718,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="6" t="inlineStr"/>
       <c r="C27" s="6" t="inlineStr"/>
@@ -20729,7 +20729,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="6" t="inlineStr"/>
       <c r="C28" s="6" t="inlineStr"/>
@@ -20740,7 +20740,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="6" t="inlineStr"/>
       <c r="C29" s="6" t="inlineStr"/>
@@ -20751,7 +20751,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="6" t="inlineStr"/>
       <c r="C30" s="6" t="inlineStr"/>
@@ -20762,7 +20762,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="6" t="inlineStr"/>
       <c r="C31" s="6" t="inlineStr"/>
@@ -20773,7 +20773,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="6" t="inlineStr"/>
       <c r="C32" s="6" t="inlineStr"/>
@@ -20784,7 +20784,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="6" t="inlineStr"/>
       <c r="C33" s="6" t="inlineStr"/>
@@ -20795,7 +20795,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="6" t="inlineStr"/>
       <c r="C34" s="6" t="inlineStr"/>
@@ -20806,7 +20806,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="6" t="inlineStr"/>
       <c r="C35" s="6" t="inlineStr"/>
@@ -20817,7 +20817,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="6" t="inlineStr"/>
       <c r="C36" s="6" t="inlineStr"/>
@@ -20828,7 +20828,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="6" t="inlineStr"/>
       <c r="C37" s="6" t="inlineStr"/>
@@ -20839,7 +20839,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="6" t="inlineStr"/>
       <c r="C38" s="6" t="inlineStr"/>
@@ -20850,7 +20850,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="6" t="inlineStr"/>
       <c r="C39" s="6" t="inlineStr"/>
@@ -20861,7 +20861,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="6" t="inlineStr"/>
       <c r="C40" s="6" t="inlineStr"/>
@@ -20872,7 +20872,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="6" t="inlineStr"/>
       <c r="C41" s="6" t="inlineStr"/>
@@ -20883,7 +20883,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="6" t="inlineStr"/>
       <c r="C42" s="6" t="inlineStr"/>
@@ -20894,7 +20894,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="6" t="inlineStr"/>
       <c r="C43" s="6" t="inlineStr"/>
@@ -20905,7 +20905,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="6" t="inlineStr"/>
       <c r="C44" s="6" t="inlineStr"/>
@@ -20916,7 +20916,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="6" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr"/>
@@ -20927,7 +20927,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="6" t="inlineStr"/>
       <c r="C46" s="6" t="inlineStr"/>
@@ -20938,7 +20938,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="6" t="inlineStr"/>
       <c r="C47" s="6" t="inlineStr"/>
@@ -20949,7 +20949,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="6" t="inlineStr"/>
       <c r="C48" s="6" t="inlineStr"/>
@@ -20960,7 +20960,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="6" t="inlineStr"/>
       <c r="C49" s="6" t="inlineStr"/>
@@ -20971,7 +20971,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="6" t="inlineStr"/>
       <c r="C50" s="6" t="inlineStr"/>
@@ -20982,7 +20982,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="6" t="inlineStr"/>
       <c r="C51" s="6" t="inlineStr"/>
@@ -20993,7 +20993,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="6" t="inlineStr"/>
       <c r="C52" s="6" t="inlineStr"/>
@@ -21004,7 +21004,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="6" t="inlineStr"/>
       <c r="C53" s="6" t="inlineStr"/>
@@ -21015,7 +21015,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="6" t="inlineStr"/>
       <c r="C54" s="6" t="inlineStr"/>
@@ -21026,7 +21026,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="6" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr"/>
@@ -21037,7 +21037,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="6" t="inlineStr"/>
       <c r="C56" s="6" t="inlineStr"/>
@@ -21048,7 +21048,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="6" t="inlineStr"/>
       <c r="C57" s="6" t="inlineStr"/>
@@ -21059,7 +21059,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="6" t="inlineStr"/>
       <c r="C58" s="6" t="inlineStr"/>
@@ -21070,7 +21070,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="6" t="inlineStr"/>
       <c r="C59" s="6" t="inlineStr"/>
@@ -21081,7 +21081,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="6" t="inlineStr"/>
       <c r="C60" s="6" t="inlineStr"/>
@@ -21092,7 +21092,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="6" t="inlineStr"/>
       <c r="C61" s="6" t="inlineStr"/>
@@ -21103,7 +21103,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="6" t="inlineStr"/>
       <c r="C62" s="6" t="inlineStr"/>
@@ -21114,7 +21114,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="6" t="inlineStr"/>
       <c r="C63" s="6" t="inlineStr"/>
@@ -21125,7 +21125,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="6" t="inlineStr"/>
       <c r="C64" s="6" t="inlineStr"/>
@@ -21136,7 +21136,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="6" t="inlineStr"/>
       <c r="C65" s="6" t="inlineStr"/>
@@ -21147,7 +21147,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="6" t="inlineStr"/>
       <c r="C66" s="6" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="6" t="inlineStr"/>
       <c r="C67" s="6" t="inlineStr"/>
@@ -21169,7 +21169,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="6" t="inlineStr"/>
       <c r="C68" s="6" t="inlineStr"/>
@@ -21240,7 +21240,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>14</v>
@@ -21261,7 +21261,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>14</v>
@@ -21284,7 +21284,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>15</v>
@@ -21307,7 +21307,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>14</v>
@@ -21330,7 +21330,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>16</v>
@@ -21353,7 +21353,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>15</v>
@@ -21376,7 +21376,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>16</v>
@@ -21399,7 +21399,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>17</v>
@@ -21422,7 +21422,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>17</v>
@@ -21445,7 +21445,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>15</v>
@@ -21468,7 +21468,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>13</v>
@@ -21491,7 +21491,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>13</v>
@@ -21512,7 +21512,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>14</v>
@@ -21535,7 +21535,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>14</v>
@@ -21558,7 +21558,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>13</v>
@@ -21579,7 +21579,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>16</v>
@@ -21602,7 +21602,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>16</v>
@@ -21625,7 +21625,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>15</v>
@@ -21646,7 +21646,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>15</v>
@@ -21667,7 +21667,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>15</v>
@@ -21688,7 +21688,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>16</v>
@@ -21711,7 +21711,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>16</v>
@@ -21734,7 +21734,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>18</v>
@@ -21757,7 +21757,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>18</v>
@@ -21780,7 +21780,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>17</v>
@@ -21801,7 +21801,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>17</v>
@@ -21824,7 +21824,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>16</v>
@@ -21845,7 +21845,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>16</v>
@@ -21868,7 +21868,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>17</v>
@@ -21891,7 +21891,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>18</v>
@@ -21914,7 +21914,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>16</v>
@@ -21937,7 +21937,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>15</v>
@@ -21958,7 +21958,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>16</v>
@@ -21981,7 +21981,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>19</v>
@@ -22004,7 +22004,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>18</v>
@@ -22027,7 +22027,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>17</v>
@@ -22050,7 +22050,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>18</v>
@@ -22073,7 +22073,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>18</v>
@@ -22094,7 +22094,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>18</v>
@@ -22117,7 +22117,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>19</v>
@@ -22140,7 +22140,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>20</v>
@@ -22163,7 +22163,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>19</v>
@@ -22186,7 +22186,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>18</v>
@@ -22209,7 +22209,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>19</v>
@@ -22232,7 +22232,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>22</v>
@@ -22255,7 +22255,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>19</v>
@@ -22278,7 +22278,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>19</v>
@@ -22301,7 +22301,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>19</v>
@@ -22324,7 +22324,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>20</v>
@@ -22347,7 +22347,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>20</v>
@@ -22370,7 +22370,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="6" t="inlineStr"/>
       <c r="C52" s="6" t="inlineStr"/>
@@ -22385,7 +22385,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="6" t="inlineStr"/>
       <c r="C53" s="6" t="inlineStr"/>
@@ -22400,7 +22400,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="6" t="inlineStr"/>
       <c r="C54" s="6" t="inlineStr"/>
@@ -22413,7 +22413,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="6" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr"/>
@@ -22428,7 +22428,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="6" t="inlineStr"/>
       <c r="C56" s="6" t="inlineStr"/>
@@ -22443,7 +22443,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="6" t="inlineStr"/>
       <c r="C57" s="6" t="inlineStr"/>
@@ -22458,7 +22458,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="6" t="inlineStr"/>
       <c r="C58" s="6" t="inlineStr"/>
@@ -22473,7 +22473,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="6" t="inlineStr"/>
       <c r="C59" s="6" t="inlineStr"/>
@@ -22488,7 +22488,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="6" t="inlineStr"/>
       <c r="C60" s="6" t="inlineStr"/>
@@ -22503,7 +22503,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="6" t="inlineStr"/>
       <c r="C61" s="6" t="inlineStr"/>
@@ -22518,7 +22518,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="6" t="inlineStr"/>
       <c r="C62" s="6" t="inlineStr"/>
@@ -22533,7 +22533,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="6" t="inlineStr"/>
       <c r="C63" s="6" t="inlineStr"/>
@@ -22548,7 +22548,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="4" t="n">
         <v>16</v>
@@ -22569,7 +22569,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="4" t="n">
         <v>17</v>
@@ -22590,7 +22590,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="4" t="n">
         <v>18</v>
@@ -22611,7 +22611,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>19</v>
@@ -22632,7 +22632,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>19</v>
@@ -22713,7 +22713,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>32</v>
@@ -22732,7 +22732,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>31</v>
@@ -22751,7 +22751,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>32</v>
@@ -22770,7 +22770,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>32</v>
@@ -22789,7 +22789,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>33</v>
@@ -22808,7 +22808,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>32</v>
@@ -22827,7 +22827,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="6" t="inlineStr"/>
       <c r="C8" s="4" t="n">
@@ -22842,7 +22842,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="6" t="inlineStr"/>
       <c r="C9" s="4" t="n">
@@ -22861,7 +22861,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="6" t="inlineStr"/>
       <c r="C10" s="4" t="n">
@@ -22878,7 +22878,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="6" t="inlineStr"/>
       <c r="C11" s="4" t="n">
@@ -22895,7 +22895,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="6" t="inlineStr"/>
       <c r="C12" s="4" t="n">
@@ -22912,7 +22912,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="6" t="inlineStr"/>
       <c r="C13" s="4" t="n">
@@ -22929,7 +22929,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>2</v>
@@ -22946,7 +22946,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="6" t="inlineStr"/>
       <c r="C15" s="4" t="n">
@@ -22961,7 +22961,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="6" t="inlineStr"/>
       <c r="C16" s="4" t="n">
@@ -22978,7 +22978,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>5</v>
@@ -22999,7 +22999,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>5</v>
@@ -23020,7 +23020,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>4</v>
@@ -23041,7 +23041,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>4</v>
@@ -23062,7 +23062,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>4</v>
@@ -23081,7 +23081,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>5</v>
@@ -23100,7 +23100,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>4</v>
@@ -23117,7 +23117,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>4</v>
@@ -23136,7 +23136,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>4</v>
@@ -23155,7 +23155,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>4</v>
@@ -23174,7 +23174,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>5</v>
@@ -23193,7 +23193,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>5</v>
@@ -23212,7 +23212,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>4</v>
@@ -23233,7 +23233,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>5</v>
@@ -23254,7 +23254,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>5</v>
@@ -23275,7 +23275,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>5</v>
@@ -23296,7 +23296,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>5</v>
@@ -23317,7 +23317,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>6</v>
@@ -23338,7 +23338,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>5</v>
@@ -23359,7 +23359,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>5</v>
@@ -23380,7 +23380,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>5</v>
@@ -23401,7 +23401,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>7</v>
@@ -23422,7 +23422,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>4</v>
@@ -23443,7 +23443,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>5</v>
@@ -23464,7 +23464,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>5</v>
@@ -23485,7 +23485,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>5</v>
@@ -23506,7 +23506,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>5</v>
@@ -23527,7 +23527,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>6</v>
@@ -23548,7 +23548,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>6</v>
@@ -23569,7 +23569,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>8</v>
@@ -23590,7 +23590,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>7</v>
@@ -23609,7 +23609,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="6" t="inlineStr"/>
       <c r="C48" s="6" t="inlineStr"/>
@@ -23620,7 +23620,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>7</v>
@@ -23641,7 +23641,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>8</v>
@@ -23662,7 +23662,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>8</v>
@@ -23683,7 +23683,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>7</v>
@@ -23704,7 +23704,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>7</v>
@@ -23723,7 +23723,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>6</v>
@@ -23744,7 +23744,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="6" t="inlineStr"/>
       <c r="C55" s="6" t="inlineStr"/>
@@ -23755,7 +23755,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="4" t="n">
         <v>7</v>
@@ -23774,7 +23774,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="4" t="n">
         <v>5</v>
@@ -23795,7 +23795,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="4" t="n">
         <v>6</v>
@@ -23816,7 +23816,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="4" t="n">
         <v>5</v>
@@ -23837,7 +23837,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="4" t="n">
         <v>4</v>
@@ -23856,7 +23856,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="4" t="n">
         <v>4</v>
@@ -23875,7 +23875,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="6" t="inlineStr"/>
       <c r="C62" s="6" t="inlineStr"/>
@@ -23886,7 +23886,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="6" t="inlineStr"/>
       <c r="C63" s="6" t="inlineStr"/>
@@ -23897,7 +23897,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="6" t="inlineStr"/>
       <c r="C64" s="6" t="inlineStr"/>
@@ -23908,7 +23908,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="6" t="inlineStr"/>
       <c r="C65" s="6" t="inlineStr"/>
@@ -23923,7 +23923,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="6" t="inlineStr"/>
       <c r="C66" s="6" t="inlineStr"/>
@@ -23938,7 +23938,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="6" t="inlineStr"/>
       <c r="C67" s="6" t="inlineStr"/>
@@ -23953,7 +23953,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="6" t="inlineStr"/>
       <c r="C68" s="6" t="inlineStr"/>
@@ -24024,7 +24024,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>11</v>
@@ -24047,7 +24047,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>12</v>
@@ -24070,7 +24070,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>11</v>
@@ -24093,7 +24093,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>11</v>
@@ -24116,7 +24116,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>13</v>
@@ -24139,7 +24139,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>13</v>
@@ -24162,7 +24162,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>14</v>
@@ -24185,7 +24185,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>14</v>
@@ -24208,7 +24208,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>14</v>
@@ -24231,7 +24231,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>11</v>
@@ -24254,7 +24254,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>10</v>
@@ -24277,7 +24277,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>11</v>
@@ -24300,7 +24300,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>12</v>
@@ -24323,7 +24323,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>13</v>
@@ -24346,7 +24346,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>10</v>
@@ -24369,7 +24369,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>15</v>
@@ -24392,7 +24392,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>13</v>
@@ -24415,7 +24415,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>11</v>
@@ -24438,7 +24438,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>11</v>
@@ -24461,7 +24461,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>11</v>
@@ -24484,7 +24484,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>12</v>
@@ -24507,7 +24507,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>13</v>
@@ -24541,7 +24541,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>7</v>
@@ -24564,7 +24564,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>6</v>
@@ -24587,7 +24587,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>5</v>
@@ -24610,7 +24610,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>5</v>
@@ -24633,7 +24633,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>8</v>
@@ -24656,7 +24656,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>8</v>
@@ -24679,7 +24679,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>7</v>
@@ -24702,7 +24702,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>5</v>
@@ -24725,7 +24725,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>5</v>
@@ -24748,7 +24748,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>6</v>
@@ -24771,7 +24771,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>9</v>
@@ -24794,7 +24794,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>9</v>
@@ -24817,7 +24817,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>6</v>
@@ -24840,7 +24840,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="6" t="inlineStr"/>
       <c r="C38" s="6" t="inlineStr"/>
@@ -24851,7 +24851,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>8</v>
@@ -24874,7 +24874,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>7</v>
@@ -24897,7 +24897,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>8</v>
@@ -24918,7 +24918,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>9</v>
@@ -24939,7 +24939,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>10</v>
@@ -24960,7 +24960,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>10</v>
@@ -24981,7 +24981,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>9</v>
@@ -25002,7 +25002,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>10</v>
@@ -25023,7 +25023,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>8</v>
@@ -25044,7 +25044,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>9</v>
@@ -25065,7 +25065,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>11</v>
@@ -25086,7 +25086,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>11</v>
@@ -25109,7 +25109,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>10</v>
@@ -25132,7 +25132,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>11</v>
@@ -25155,7 +25155,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>9</v>
@@ -25178,7 +25178,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
@@ -25201,7 +25201,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="4" t="n">
         <v>7</v>
@@ -25224,7 +25224,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="4" t="n">
         <v>8</v>
@@ -25247,7 +25247,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="4" t="n">
         <v>11</v>
@@ -25270,7 +25270,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="4" t="n">
         <v>11</v>
@@ -25293,7 +25293,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="4" t="n">
         <v>10</v>
@@ -25316,7 +25316,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="4" t="n">
         <v>10</v>
@@ -25339,7 +25339,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="4" t="n">
         <v>8</v>
@@ -25362,7 +25362,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="4" t="n">
         <v>9</v>
@@ -25385,7 +25385,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="4" t="n">
         <v>8</v>
@@ -25408,7 +25408,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="4" t="n">
         <v>8</v>
@@ -25431,7 +25431,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="6" t="inlineStr"/>
       <c r="C65" s="6" t="inlineStr"/>
@@ -25442,7 +25442,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="6" t="inlineStr"/>
       <c r="C66" s="6" t="inlineStr"/>
@@ -25453,7 +25453,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>9</v>
@@ -25476,7 +25476,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>8</v>
@@ -25559,7 +25559,7 @@
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="n">
-        <v>46023</v>
+        <v>45658</v>
       </c>
       <c r="B2" s="4" t="n">
         <v>7</v>
@@ -25578,7 +25578,7 @@
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B3" s="4" t="n">
         <v>4</v>
@@ -25597,7 +25597,7 @@
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>46025</v>
+        <v>45660</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>4</v>
@@ -25616,7 +25616,7 @@
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>46026</v>
+        <v>45661</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
@@ -25635,7 +25635,7 @@
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>46027</v>
+        <v>45662</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>6</v>
@@ -25654,7 +25654,7 @@
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>3</v>
@@ -25673,7 +25673,7 @@
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>4</v>
@@ -25692,7 +25692,7 @@
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>6</v>
@@ -25711,7 +25711,7 @@
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>7</v>
@@ -25730,7 +25730,7 @@
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>46032</v>
+        <v>45667</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>4</v>
@@ -25749,7 +25749,7 @@
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>46033</v>
+        <v>45668</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
@@ -25768,7 +25768,7 @@
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>46034</v>
+        <v>45669</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>3</v>
@@ -25787,7 +25787,7 @@
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>3</v>
@@ -25806,7 +25806,7 @@
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>3</v>
@@ -25825,7 +25825,7 @@
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>2</v>
@@ -25844,7 +25844,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>6</v>
@@ -25863,7 +25863,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>46039</v>
+        <v>45674</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>5</v>
@@ -25882,7 +25882,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>46040</v>
+        <v>45675</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>2</v>
@@ -25901,7 +25901,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>46041</v>
+        <v>45676</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>4</v>
@@ -25920,7 +25920,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>46042</v>
+        <v>45677</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>6</v>
@@ -25939,7 +25939,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>5</v>
@@ -25958,7 +25958,7 @@
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>5</v>
@@ -25977,7 +25977,7 @@
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>6</v>
@@ -25996,7 +25996,7 @@
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>46046</v>
+        <v>45681</v>
       </c>
       <c r="B25" s="4" t="n">
         <v>6</v>
@@ -26015,7 +26015,7 @@
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>46047</v>
+        <v>45682</v>
       </c>
       <c r="B26" s="4" t="n">
         <v>7</v>
@@ -26034,7 +26034,7 @@
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>46048</v>
+        <v>45683</v>
       </c>
       <c r="B27" s="4" t="n">
         <v>7</v>
@@ -26053,7 +26053,7 @@
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B28" s="4" t="n">
         <v>7</v>
@@ -26072,7 +26072,7 @@
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>6</v>
@@ -26091,7 +26091,7 @@
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B30" s="4" t="n">
         <v>9</v>
@@ -26110,7 +26110,7 @@
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>46052</v>
+        <v>45687</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>7</v>
@@ -26129,7 +26129,7 @@
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>46053</v>
+        <v>45688</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>5</v>
@@ -26148,7 +26148,7 @@
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>46054</v>
+        <v>45689</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>6</v>
@@ -26165,7 +26165,7 @@
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>46055</v>
+        <v>45690</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>6</v>
@@ -26182,7 +26182,7 @@
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>46056</v>
+        <v>45691</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>7</v>
@@ -26201,7 +26201,7 @@
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>45692</v>
       </c>
       <c r="B36" s="4" t="n">
         <v>5</v>
@@ -26220,7 +26220,7 @@
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>46058</v>
+        <v>45693</v>
       </c>
       <c r="B37" s="4" t="n">
         <v>5</v>
@@ -26239,7 +26239,7 @@
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>46059</v>
+        <v>45694</v>
       </c>
       <c r="B38" s="4" t="n">
         <v>6</v>
@@ -26260,7 +26260,7 @@
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="3" t="n">
-        <v>46060</v>
+        <v>45695</v>
       </c>
       <c r="B39" s="4" t="n">
         <v>5</v>
@@ -26279,7 +26279,7 @@
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="3" t="n">
-        <v>46061</v>
+        <v>45696</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>6</v>
@@ -26300,7 +26300,7 @@
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="3" t="n">
-        <v>46062</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="4" t="n">
         <v>6</v>
@@ -26321,7 +26321,7 @@
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="3" t="n">
-        <v>46063</v>
+        <v>45698</v>
       </c>
       <c r="B42" s="4" t="n">
         <v>9</v>
@@ -26342,7 +26342,7 @@
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="3" t="n">
-        <v>46064</v>
+        <v>45699</v>
       </c>
       <c r="B43" s="4" t="n">
         <v>7</v>
@@ -26363,7 +26363,7 @@
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="3" t="n">
-        <v>46065</v>
+        <v>45700</v>
       </c>
       <c r="B44" s="4" t="n">
         <v>7</v>
@@ -26384,7 +26384,7 @@
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="3" t="n">
-        <v>46066</v>
+        <v>45701</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>9</v>
@@ -26405,7 +26405,7 @@
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="3" t="n">
-        <v>46067</v>
+        <v>45702</v>
       </c>
       <c r="B46" s="4" t="n">
         <v>11</v>
@@ -26426,7 +26426,7 @@
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="3" t="n">
-        <v>46068</v>
+        <v>45703</v>
       </c>
       <c r="B47" s="4" t="n">
         <v>9</v>
@@ -26447,7 +26447,7 @@
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>45704</v>
       </c>
       <c r="B48" s="4" t="n">
         <v>9</v>
@@ -26468,7 +26468,7 @@
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="3" t="n">
-        <v>46070</v>
+        <v>45705</v>
       </c>
       <c r="B49" s="4" t="n">
         <v>8</v>
@@ -26489,7 +26489,7 @@
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="3" t="n">
-        <v>46071</v>
+        <v>45706</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>9</v>
@@ -26510,7 +26510,7 @@
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="3" t="n">
-        <v>46072</v>
+        <v>45707</v>
       </c>
       <c r="B51" s="4" t="n">
         <v>11</v>
@@ -26531,7 +26531,7 @@
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="3" t="n">
-        <v>46073</v>
+        <v>45708</v>
       </c>
       <c r="B52" s="4" t="n">
         <v>11</v>
@@ -26552,7 +26552,7 @@
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="3" t="n">
-        <v>46074</v>
+        <v>45709</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>9</v>
@@ -26573,7 +26573,7 @@
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="3" t="n">
-        <v>46075</v>
+        <v>45710</v>
       </c>
       <c r="B54" s="4" t="n">
         <v>7</v>
@@ -26592,7 +26592,7 @@
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="3" t="n">
-        <v>46076</v>
+        <v>45711</v>
       </c>
       <c r="B55" s="4" t="n">
         <v>7</v>
@@ -26611,7 +26611,7 @@
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="3" t="n">
-        <v>46077</v>
+        <v>45712</v>
       </c>
       <c r="B56" s="4" t="n">
         <v>10</v>
@@ -26630,7 +26630,7 @@
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="3" t="n">
-        <v>46078</v>
+        <v>45713</v>
       </c>
       <c r="B57" s="4" t="n">
         <v>10</v>
@@ -26651,7 +26651,7 @@
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="3" t="n">
-        <v>46079</v>
+        <v>45714</v>
       </c>
       <c r="B58" s="4" t="n">
         <v>10</v>
@@ -26672,7 +26672,7 @@
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="3" t="n">
-        <v>46080</v>
+        <v>45715</v>
       </c>
       <c r="B59" s="4" t="n">
         <v>9</v>
@@ -26693,7 +26693,7 @@
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="3" t="n">
-        <v>46081</v>
+        <v>45716</v>
       </c>
       <c r="B60" s="4" t="n">
         <v>9</v>
@@ -26714,7 +26714,7 @@
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="3" t="n">
-        <v>46082</v>
+        <v>45717</v>
       </c>
       <c r="B61" s="4" t="n">
         <v>8</v>
@@ -26735,7 +26735,7 @@
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="3" t="n">
-        <v>46083</v>
+        <v>45718</v>
       </c>
       <c r="B62" s="4" t="n">
         <v>9</v>
@@ -26756,7 +26756,7 @@
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="3" t="n">
-        <v>46084</v>
+        <v>45719</v>
       </c>
       <c r="B63" s="4" t="n">
         <v>10</v>
@@ -26775,7 +26775,7 @@
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="3" t="n">
-        <v>46085</v>
+        <v>45720</v>
       </c>
       <c r="B64" s="4" t="n">
         <v>11</v>
@@ -26796,7 +26796,7 @@
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="3" t="n">
-        <v>46086</v>
+        <v>45721</v>
       </c>
       <c r="B65" s="4" t="n">
         <v>10</v>
@@ -26815,7 +26815,7 @@
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="3" t="n">
-        <v>46087</v>
+        <v>45722</v>
       </c>
       <c r="B66" s="4" t="n">
         <v>11</v>
@@ -26836,7 +26836,7 @@
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="3" t="n">
-        <v>46088</v>
+        <v>45723</v>
       </c>
       <c r="B67" s="4" t="n">
         <v>12</v>
@@ -26857,7 +26857,7 @@
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="3" t="n">
-        <v>46089</v>
+        <v>45724</v>
       </c>
       <c r="B68" s="4" t="n">
         <v>12</v>
